--- a/nrf/applications/LL311_BLE/doc/pin_assignment.xlsx
+++ b/nrf/applications/LL311_BLE/doc/pin_assignment.xlsx
@@ -468,13 +468,16 @@
     <t>P1.14</t>
   </si>
   <si>
-    <t>VBATT_NTC</t>
-  </si>
-  <si>
-    <t>电池温度检测</t>
-  </si>
-  <si>
-    <t>只在充电的时候硬线路才会使能，才需要去监测ADC</t>
+    <t>NFC_NPD</t>
+  </si>
+  <si>
+    <t>NFC模块硬件复位信号</t>
+  </si>
+  <si>
+    <t>默认低电平（关断）</t>
+  </si>
+  <si>
+    <t>NFC模块上电后</t>
   </si>
   <si>
     <t>P2.00</t>
@@ -508,9 +511,6 @@
   </si>
   <si>
     <t>4G模块电源控制信号</t>
-  </si>
-  <si>
-    <t>默认低电平（关断）</t>
   </si>
   <si>
     <t>关闭输入缓冲</t>
@@ -2449,10 +2449,10 @@
         <v>123</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>118</v>
+        <v>57</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>12</v>
@@ -2461,80 +2461,80 @@
         <v>32</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:8">
       <c r="A24" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:8">
       <c r="A25" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:8">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>137</v>
@@ -2554,13 +2554,13 @@
         <v>57</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>137</v>
@@ -2580,13 +2580,13 @@
         <v>57</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>137</v>
@@ -2606,13 +2606,13 @@
         <v>57</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>137</v>
@@ -2632,13 +2632,13 @@
         <v>57</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>137</v>
@@ -2664,7 +2664,7 @@
         <v>15</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>154</v>
@@ -2690,7 +2690,7 @@
         <v>15</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>154</v>
@@ -2716,7 +2716,7 @@
         <v>15</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>154</v>
@@ -2742,7 +2742,7 @@
         <v>15</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>154</v>
@@ -2765,10 +2765,10 @@
         <v>163</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>164</v>
